--- a/ig/main/CodeSystem-tre-r401-activite-sociale-regulee.xlsx
+++ b/ig/main/CodeSystem-tre-r401-activite-sociale-regulee.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260223120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T12:00:00.000+00:00</t>
+    <t>2026-03-30T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -466,7 +466,7 @@
     <t>259</t>
   </si>
   <si>
-    <t>Activ.Club et Équipe de Prévention</t>
+    <t>Prévention spécialisée</t>
   </si>
   <si>
     <t>262</t>

--- a/ig/main/CodeSystem-tre-r401-activite-sociale-regulee.xlsx
+++ b/ig/main/CodeSystem-tre-r401-activite-sociale-regulee.xlsx
@@ -85,7 +85,12 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Cette TRE hiérarchique remplace les TRE_R280-DisciplineEquipementSocial, TRE_R298-AgregatDisciplineEquipSocNiv1, TRE_R299-AgregatDisciplineEquipSocNiv2, TRE_R300-AgregatDisciplineEquipSocNiv3 et l'ASS_X14_AgregatDisciplineEquipementSocial. Cette TRE possède des propriétés spécifiques : le niveau d'agrégat desASOCR de 1 à 4 (du plus large au plus fin), le parent d'un agrégat d'ASOCR ou d'une ASOCR ainsi que les relations nécessaires à la construction des JDV dynamiques associés</t>
+    <t>Cette TRE hiérarchique remplace les éléments suivants :
+TRE_R280-DisciplineEquipementSocial, TRE_R298-AgregatDisciplineEquipSocNiv1, TRE_R299-AgregatDisciplineEquipSocNiv2, TRE_R300-AgregatDisciplineEquipSocNiv3 et ASS_X14_AgregatDisciplineEquipementSocial.
+Cette TRE possède des propriétés spécifiques :
+1. Le niveau d'agrégat des ASOCR de 1 à 4 (du plus large au plus fin)
+2. Le parent d'un agrégat d'ASOCR ou d'une ASOCR
+3. Les relations nécessaires à la construction des JDV dynamiques associés</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/main/CodeSystem-tre-r401-activite-sociale-regulee.xlsx
+++ b/ig/main/CodeSystem-tre-r401-activite-sociale-regulee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="404">
   <si>
     <t>Property</t>
   </si>
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r401-activite-sociale-regulee</t>
+    <t>http://example.org/CodeSystem/tre-r401-activite-sociale-regulee</t>
   </si>
   <si>
     <t>Identifier</t>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00.000+00:00</t>
+    <t>2026-06-01T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -129,7 +129,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>164</t>
+    <t>165</t>
   </si>
   <si>
     <t>Code</t>
@@ -712,6 +712,21 @@
   </si>
   <si>
     <t>Centre de Vie pour Cas lourds</t>
+  </si>
+  <si>
+    <t>570</t>
+  </si>
+  <si>
+    <t>Unités résidentielles pour cas complexes</t>
+  </si>
+  <si>
+    <t>Ces unités ont le statut de MAS et sont adossées à des établissements médico-sociaux pour adultes handicapés existants mentionnés au 7° de l’article L.312-1 du CASF.
+Le fonctionnement et l’organisation des URTSA :
+- Ces unités ont une haute intensité de prise en charge des patients, avec des pathologies lourdes.
+- La création de ces unités nécessite des locaux spécifiques adaptés à l'accueil de ce public.
+- Le public ne peut pas être accueilli dans les locaux dans lesquels sont accueillis les autres publics car les personnes accueillies dans ces unités présentent des troubles majeurs du comportement et nécessitent un accompagnement spécifique, de très grande proximité, un écosystème sécurisé, une architecture adaptée et des professionnels experts notamment formés à la gestion de crise.
+- Ce sont généralement des très petites unités de vie avec deux unités de trois places ou trois unités de deux places au sein d'un unique bâtiment. Cette configuration permet d’avoir des espaces de vie collective et des espaces de prise en charge individuelle pour isoler les résidents du collectif.
+- L’accueil prévu est de 6 personnes.</t>
   </si>
   <si>
     <t>589</t>
@@ -1683,7 +1698,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D165"/>
+  <dimension ref="A1:D166"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2646,17 +2661,19 @@
       <c r="C80" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="D80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>233</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
         <v>74</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D81" s="2"/>
     </row>
@@ -2665,10 +2682,10 @@
         <v>74</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D82" s="2"/>
     </row>
@@ -2677,10 +2694,10 @@
         <v>74</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D83" s="2"/>
     </row>
@@ -2689,10 +2706,10 @@
         <v>74</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D84" s="2"/>
     </row>
@@ -2701,10 +2718,10 @@
         <v>74</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D85" s="2"/>
     </row>
@@ -2713,10 +2730,10 @@
         <v>74</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D86" s="2"/>
     </row>
@@ -2725,10 +2742,10 @@
         <v>74</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D87" s="2"/>
     </row>
@@ -2737,10 +2754,10 @@
         <v>74</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D88" s="2"/>
     </row>
@@ -2749,7 +2766,7 @@
         <v>74</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C89" t="s" s="2">
         <v>249</v>
@@ -2761,10 +2778,10 @@
         <v>74</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D90" s="2"/>
     </row>
@@ -2773,10 +2790,10 @@
         <v>74</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D91" s="2"/>
     </row>
@@ -2785,10 +2802,10 @@
         <v>74</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D92" s="2"/>
     </row>
@@ -2797,10 +2814,10 @@
         <v>74</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D93" s="2"/>
     </row>
@@ -2809,10 +2826,10 @@
         <v>74</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D94" s="2"/>
     </row>
@@ -2821,10 +2838,10 @@
         <v>74</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D95" s="2"/>
     </row>
@@ -2833,10 +2850,10 @@
         <v>74</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D96" s="2"/>
     </row>
@@ -2845,10 +2862,10 @@
         <v>74</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D97" s="2"/>
     </row>
@@ -2857,10 +2874,10 @@
         <v>74</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D98" s="2"/>
     </row>
@@ -2869,10 +2886,10 @@
         <v>74</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D99" s="2"/>
     </row>
@@ -2881,10 +2898,10 @@
         <v>74</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D100" s="2"/>
     </row>
@@ -2893,10 +2910,10 @@
         <v>74</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D101" s="2"/>
     </row>
@@ -2905,10 +2922,10 @@
         <v>74</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D102" s="2"/>
     </row>
@@ -2917,10 +2934,10 @@
         <v>74</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D103" s="2"/>
     </row>
@@ -2929,10 +2946,10 @@
         <v>74</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D104" s="2"/>
     </row>
@@ -2941,10 +2958,10 @@
         <v>74</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D105" s="2"/>
     </row>
@@ -2953,10 +2970,10 @@
         <v>74</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D106" s="2"/>
     </row>
@@ -2965,10 +2982,10 @@
         <v>74</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D107" s="2"/>
     </row>
@@ -2977,10 +2994,10 @@
         <v>74</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D108" s="2"/>
     </row>
@@ -2989,10 +3006,10 @@
         <v>74</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D109" s="2"/>
     </row>
@@ -3001,10 +3018,10 @@
         <v>74</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D110" s="2"/>
     </row>
@@ -3013,10 +3030,10 @@
         <v>74</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D111" s="2"/>
     </row>
@@ -3025,10 +3042,10 @@
         <v>74</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D112" s="2"/>
     </row>
@@ -3037,10 +3054,10 @@
         <v>74</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D113" s="2"/>
     </row>
@@ -3049,10 +3066,10 @@
         <v>74</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D114" s="2"/>
     </row>
@@ -3061,10 +3078,10 @@
         <v>74</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D115" s="2"/>
     </row>
@@ -3073,10 +3090,10 @@
         <v>74</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D116" s="2"/>
     </row>
@@ -3085,10 +3102,10 @@
         <v>74</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>102</v>
+        <v>306</v>
       </c>
       <c r="D117" s="2"/>
     </row>
@@ -3097,10 +3114,10 @@
         <v>74</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>306</v>
+        <v>102</v>
       </c>
       <c r="D118" s="2"/>
     </row>
@@ -3109,10 +3126,10 @@
         <v>74</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D119" s="2"/>
     </row>
@@ -3121,10 +3138,10 @@
         <v>74</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D120" s="2"/>
     </row>
@@ -3133,10 +3150,10 @@
         <v>74</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D121" s="2"/>
     </row>
@@ -3145,10 +3162,10 @@
         <v>74</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D122" s="2"/>
     </row>
@@ -3157,10 +3174,10 @@
         <v>74</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D123" s="2"/>
     </row>
@@ -3169,10 +3186,10 @@
         <v>74</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D124" s="2"/>
     </row>
@@ -3181,10 +3198,10 @@
         <v>74</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D125" s="2"/>
     </row>
@@ -3193,10 +3210,10 @@
         <v>74</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D126" s="2"/>
     </row>
@@ -3205,10 +3222,10 @@
         <v>74</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D127" s="2"/>
     </row>
@@ -3217,10 +3234,10 @@
         <v>74</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D128" s="2"/>
     </row>
@@ -3229,10 +3246,10 @@
         <v>74</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D129" s="2"/>
     </row>
@@ -3241,10 +3258,10 @@
         <v>74</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D130" s="2"/>
     </row>
@@ -3253,10 +3270,10 @@
         <v>74</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D131" s="2"/>
     </row>
@@ -3265,10 +3282,10 @@
         <v>74</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D132" s="2"/>
     </row>
@@ -3277,10 +3294,10 @@
         <v>74</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D133" s="2"/>
     </row>
@@ -3289,10 +3306,10 @@
         <v>74</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D134" s="2"/>
     </row>
@@ -3301,10 +3318,10 @@
         <v>74</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D135" s="2"/>
     </row>
@@ -3313,10 +3330,10 @@
         <v>74</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D136" s="2"/>
     </row>
@@ -3325,10 +3342,10 @@
         <v>74</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D137" s="2"/>
     </row>
@@ -3337,10 +3354,10 @@
         <v>74</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D138" s="2"/>
     </row>
@@ -3349,10 +3366,10 @@
         <v>74</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D139" s="2"/>
     </row>
@@ -3361,10 +3378,10 @@
         <v>74</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D140" s="2"/>
     </row>
@@ -3373,10 +3390,10 @@
         <v>74</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D141" s="2"/>
     </row>
@@ -3385,10 +3402,10 @@
         <v>74</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D142" s="2"/>
     </row>
@@ -3397,10 +3414,10 @@
         <v>74</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D143" s="2"/>
     </row>
@@ -3409,10 +3426,10 @@
         <v>74</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D144" s="2"/>
     </row>
@@ -3421,10 +3438,10 @@
         <v>74</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D145" s="2"/>
     </row>
@@ -3433,10 +3450,10 @@
         <v>74</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D146" s="2"/>
     </row>
@@ -3445,10 +3462,10 @@
         <v>74</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D147" s="2"/>
     </row>
@@ -3457,10 +3474,10 @@
         <v>74</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D148" s="2"/>
     </row>
@@ -3469,10 +3486,10 @@
         <v>74</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D149" s="2"/>
     </row>
@@ -3481,10 +3498,10 @@
         <v>74</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D150" s="2"/>
     </row>
@@ -3493,10 +3510,10 @@
         <v>74</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D151" s="2"/>
     </row>
@@ -3505,10 +3522,10 @@
         <v>74</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D152" s="2"/>
     </row>
@@ -3517,10 +3534,10 @@
         <v>74</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D153" s="2"/>
     </row>
@@ -3529,10 +3546,10 @@
         <v>74</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D154" s="2"/>
     </row>
@@ -3541,10 +3558,10 @@
         <v>74</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D155" s="2"/>
     </row>
@@ -3553,10 +3570,10 @@
         <v>74</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D156" s="2"/>
     </row>
@@ -3565,10 +3582,10 @@
         <v>74</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D157" s="2"/>
     </row>
@@ -3577,10 +3594,10 @@
         <v>74</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D158" s="2"/>
     </row>
@@ -3589,10 +3606,10 @@
         <v>74</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D159" s="2"/>
     </row>
@@ -3601,10 +3618,10 @@
         <v>74</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D160" s="2"/>
     </row>
@@ -3613,10 +3630,10 @@
         <v>74</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D161" s="2"/>
     </row>
@@ -3625,10 +3642,10 @@
         <v>74</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D162" s="2"/>
     </row>
@@ -3637,10 +3654,10 @@
         <v>74</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D163" s="2"/>
     </row>
@@ -3649,10 +3666,10 @@
         <v>74</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D164" s="2"/>
     </row>
@@ -3661,12 +3678,24 @@
         <v>74</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D165" s="2"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C166" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="D166" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/main/CodeSystem-tre-r401-activite-sociale-regulee.xlsx
+++ b/ig/main/CodeSystem-tre-r401-activite-sociale-regulee.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/CodeSystem/tre-r401-activite-sociale-regulee</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r401-activite-sociale-regulee</t>
   </si>
   <si>
     <t>Identifier</t>
